--- a/supervisor_package/analysis_files/SME_Datapoint_Guide.xlsx
+++ b/supervisor_package/analysis_files/SME_Datapoint_Guide.xlsx
@@ -4,60 +4,75 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datapoint guide" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enabling instruments" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datapoint guide'!$A$1:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enabling instruments'!$A$1:$D$15</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF475569"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF2E8B57"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,7 +82,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D5A80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,143 +105,147 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFDCE1E8"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFDCE1E8"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFDCE1E8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFDCE1E8"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E79"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -252,231 +280,502 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" style="5" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="6">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>This workbook supports the "Seafood SME Sustainability Priority Navigator" tool, a companion to the thesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="6">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>"Navigating the Sustainability Disclosure Ecosystem: A diagnostic framework for European seafood processing SMEs."</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="6">
-      <c r="A3" s="7" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="6">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Column sourcing:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="23.85" customHeight="1" s="6">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>- Topic / Datapoint (official name) / Source standard / Official reference: taken verbatim from the VSME Standard, official ESRS datapoint list, and the GDST Standard -- same sourcing as thesis Chapter 7s coverage matrix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="23.85" customHeight="1" s="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>- What this means in practice / How to start collecting it: written for this tool to make the official wording actionable for a seafood-processing SME; these are plain-language explanations of the official requirement, not new requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="23.85" customHeight="1" s="6">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>- Enabling instruments: drawn only from instruments already catalogued in the thesiss own necessity-domain matrix (Appendix A / Chapter 5), matched per topic rather than by a generic prefix rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="6">
-      <c r="A8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="6">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Built 2026-07-15. Flag any row that looks wrong -- this is a first pass, not yet reviewed line by line.</t>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SME DATAPOINT GUIDE — what to collect, and how to start</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Supporting file for Chapter 6 of "Build Once, Answer Many: Where Disclosure Demand Converges for European Seafood-Processing SMEs" (L. Verhoeven, EPFL 2026). Snapshot June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>WHAT THIS FILE IS</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>The data layer beneath the build-first themes: for every topic in the demand matrix, the specific datapoints a firm has to produce, what each one means in plain language, and where to get it. This is the source behind the diagnostic tool's topic pages and its Excel download.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>THE SHEETS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Datapoint guide</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>112 datapoints across 32 topics. One row per datapoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Enabling instruments</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>14 methods, management systems and data standards that help produce the data. These are excluded from the demand counts because they do not themselves ask for a disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>COLUMNS IN "DATAPOINT GUIDE"</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Topic / Topic code</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>The disclosure topic, and its ESRS code where one exists. Four seafood topics have no ESRS code and are sourced from GRI 13 instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Datapoint (official name)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>The name as it appears in the source standard — use this when talking to an auditor or a customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>What this means in practice</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>The same thing in plain language. Written for someone who has not read the standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>How to start collecting it</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>The realistic first step: which invoice, log, certificate or supplier to go to. Not a full method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Source standard</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>ESRS, VSME, GDST or GRI. VSME rows are the lighter, self-assessable version of an ESRS requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Official reference</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>The exact clause, so any row can be checked against the primary source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Enabling instruments</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Which Layer 2 method or system produces this data, where one applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>HOW TO USE IT</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Start from your build-first topics (Chapter 6, or the diagnostic tool), filter this sheet to those topics, and work down the "How to start collecting it" column. The datapoints are listed per topic, not in priority order within a topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Both the ESRS and the VSME are under active Omnibus revision. This is a dated snapshot; the revised standards adopted on 3 July 2026 renumber several requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>"How to start collecting it" is practical guidance, not an assurance-grade method. It tells a firm where to begin, not how to satisfy an auditor.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H113"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="5" min="1" max="1"/>
-    <col width="10" customWidth="1" style="5" min="2" max="2"/>
-    <col width="32" customWidth="1" style="5" min="3" max="3"/>
-    <col width="42" customWidth="1" style="5" min="4" max="5"/>
-    <col width="10" customWidth="1" style="5" min="6" max="6"/>
-    <col width="16" customWidth="1" style="5" min="7" max="7"/>
-    <col width="30" customWidth="1" style="5" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.85" customHeight="1" s="6">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Topic</t>
@@ -518,7 +817,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="57.45" customHeight="1" s="6">
+    <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Climate transition actions (E1-3)</t>
@@ -544,7 +843,7 @@
           <t>List the concrete actions already under way (from your energy/operations team) and categorise each using the standard levers (energy efficiency, fuel switching, electrification, etc.) — no new data, just labelling what you already do.</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -560,7 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="35.05" customHeight="1" s="6">
+    <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Climate transition actions (E1-3)</t>
@@ -586,7 +885,7 @@
           <t>Compare this year’s Scope 1+2 figure (from your E1-6 data) against your baseline year’s figure.</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -602,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="35.05" customHeight="1" s="6">
+    <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Climate transition actions (E1-3)</t>
@@ -628,7 +927,7 @@
           <t>An internal estimate from whoever manages your energy/operations investments — a forecast, not a measurement.</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -644,7 +943,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="35.05" customHeight="1" s="6">
+    <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Climate transition actions (E1-3)</t>
@@ -670,7 +969,7 @@
           <t>A short written note from management; no data collection, just an honest statement of constraints.</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -686,175 +985,175 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46.25" customHeight="1" s="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>GHG reduction targets (E1-4)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>E1-4</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Disclosure of whether and how GHG emissions reduction targets and (or)…</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Whether you have set a formal target to reduce emissions (e.g. "-30% by 2030"), and how it was decided.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>A management decision to document, not a data-collection exercise — if no target exists yet, this is the trigger to set one (see SBTi or your customer’s own target as a benchmark).</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>ESRS E1-4_01</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="46.25" customHeight="1" s="6">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>GHG reduction targets (E1-4)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>E1-4</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Tables: Multiple Dimensions (baseline year and targets; GHG Types, Sco…</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>The technical detail behind your target: which base year you compare against, which gases and scope-3 categories are covered, and how you measure intensity (e.g. per tonne of product).</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Filled in once you have set the target above — mostly definitional choices your consultant or the ESRS/VSME template will guide you through.</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>ESRS E1-4_02</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="23.85" customHeight="1" s="6">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>GHG reduction targets (E1-4)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>E1-4</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Absolute value of total Greenhouse gas emissions reduction</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>The actual tonnes of CO2-equivalent your emissions have fallen by since the baseline year.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Same Scope 1+2 (and Scope 3 if tracked) data as E1-6, compared year-on-year.</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>ESRS E1-4_03</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="23.85" customHeight="1" s="6">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>GHG reduction targets (E1-4)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>E1-4</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Percentage of total Greenhouse gas emissions reduction (as of emission…</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>The same reduction expressed as a percentage of your baseline-year emissions.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>A calculation from the figure above — no new data.</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>ESRS E1-4_04</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="46.25" customHeight="1" s="6">
+    <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Energy use &amp; mix (E1-5)</t>
@@ -880,7 +1179,7 @@
           <t>Pull the renewable share from your electricity supplier’s invoices or their "fuel mix" / green-tariff certificate; most EU suppliers state this on the bill or on request.</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -896,7 +1195,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="35.05" customHeight="1" s="6">
+    <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Energy use &amp; mix (E1-5)</t>
@@ -922,7 +1221,7 @@
           <t>Same utility bills as above — subtract the renewable share, or ask your supplier for a fuel-mix breakdown.</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -938,7 +1237,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46.25" customHeight="1" s="6">
+    <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Energy use &amp; mix (E1-5)</t>
@@ -964,7 +1263,7 @@
           <t>Add up fuel purchase volumes (litres/m³) from supplier invoices or fuel-card records, converted to energy units (kWh/GJ) using standard conversion factors (e.g. UK DEFRA or IEA factors).</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -980,7 +1279,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="35.05" customHeight="1" s="6">
+    <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Energy use &amp; mix (E1-5)</t>
@@ -1006,7 +1305,7 @@
           <t>This is simply the sum of the three rows above — no separate data collection needed once you have those.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -1022,133 +1321,133 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="68.65000000000001" customHeight="1" s="6">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>GHG emissions (E1-6)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>E1-6</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Scope 1 GHG emissions</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Emissions from sources you own or control directly — your own boilers, vehicles, generators, on-site refrigerant leaks.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Take your fuel and refrigerant-top-up volumes (from the E1-5 fuel data plus refrigerant purchase/service records) and apply the GHG Protocol Corporate Standard’s emission factors; free calculators (e.g. from your national environment agency) do this conversion for you.</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>VSME B3-6 §30(a)</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="46.25" customHeight="1" s="6">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>GHG emissions (E1-6)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>E1-6</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Scope 2 GHG emissions (location-based)</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Emissions associated with the electricity you buy, calculated using the average emissions factor of your national grid (not your specific green-tariff choice).</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Multiply your total purchased-electricity volume (kWh, from E1-5) by your country’s published grid emission factor (national statistics office or IEA); many utility bills also show this directly.</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>VSME B3-7 §30(b)</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="35.05" customHeight="1" s="6">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>GHG emissions (E1-6)</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>E1-6</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>GHG intensity</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Your total emissions divided by your turnover — a way to compare emissions per euro of revenue, regardless of company size.</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Once you have Scope 1 + Scope 2 above, divide by your annual turnover in EUR — a single calculation, not a new data source.</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>VSME B3-8 §31</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>GHG Protocol, ISO 14064</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="46.25" customHeight="1" s="6">
+    <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Water policy (E3-1)</t>
@@ -1174,7 +1473,7 @@
           <t>Check whether you already have an environmental or water policy document; if yes, confirm it covers this specific point, if no, this flags a policy gap to close rather than a figure to measure.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1190,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="46.25" customHeight="1" s="6">
+    <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Water policy (E3-1)</t>
@@ -1216,7 +1515,7 @@
           <t>Check whether you already have an environmental or water policy document; if yes, confirm it covers this specific point, if no, this flags a policy gap to close rather than a figure to measure.</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1232,7 +1531,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="46.25" customHeight="1" s="6">
+    <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Water policy (E3-1)</t>
@@ -1258,7 +1557,7 @@
           <t>Check whether you already have an environmental or water policy document; if yes, confirm it covers this specific point, if no, this flags a policy gap to close rather than a figure to measure.</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1274,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="46.25" customHeight="1" s="6">
+    <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Water policy (E3-1)</t>
@@ -1300,7 +1599,7 @@
           <t>Check whether you already have an environmental or water policy document; if yes, confirm it covers this specific point, if no, this flags a policy gap to close rather than a figure to measure.</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1316,133 +1615,133 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="46.25" customHeight="1" s="6">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Water actions (E3-2)</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>E3-2</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Layer in mitigation hierarchy to which action and resources can be all…</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Where your water actions sit on the standard "avoid → reduce → restore" ladder used in environmental management.</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>A classification exercise by whoever runs your environmental actions — match your existing initiatives to the standard mitigation-hierarchy categories.</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>ESRS E3-2_01</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="35.05" customHeight="1" s="6">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Water actions (E3-2)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>E3-2</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Information about specific collective action for water and marine reso…</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Any joint action you take together with others (e.g. an industry water-stewardship initiative) rather than alone.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>From your sustainability/operations team — report only if such collective action exists.</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>ESRS E3-2_02</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="35.05" customHeight="1" s="6">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Water actions (E3-2)</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>E3-2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Disclosure of actions and resources in relation to areas at water risk</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>What you are doing, and what you are investing, specifically at sites located in water-stressed areas.</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Cross-reference your E3-4 water-stress site list with whatever action/budget your operations team already has for those sites.</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>ESRS E3-2_03</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="23.85" customHeight="1" s="6">
+    <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Water targets (E3-3)</t>
@@ -1468,7 +1767,7 @@
           <t>A policy/target-design question for management — confirm the target explicitly names those sites.</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1484,7 +1783,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="23.85" customHeight="1" s="6">
+    <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Water targets (E3-3)</t>
@@ -1510,7 +1809,7 @@
           <t>Same target-design check as above.</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1526,7 +1825,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="23.85" customHeight="1" s="6">
+    <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Water targets (E3-3)</t>
@@ -1552,7 +1851,7 @@
           <t>Same target-design check — compare your target wording to your E3-4 water-consumption figure.</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1568,7 +1867,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="35.05" customHeight="1" s="6">
+    <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Water targets (E3-3)</t>
@@ -1594,7 +1893,7 @@
           <t>Check your operating permits/licences — if a regulator sets a water-use limit, mark this as legally mandatory.</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1610,133 +1909,133 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="46.25" customHeight="1" s="6">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Water consumption (E3-4)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>E3-4</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Total water withdrawal</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>How much water you drew into your site from any source (mains supply, borehole, river, rainwater).</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Read off your water utility invoices (m³) for mains supply; add metered volumes for any borehole or self-abstracted water if you have your own permit/meter.</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>VSME B6-1 §35</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="46.25" customHeight="1" s="6">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Water consumption (E3-4)</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>E3-4</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Water withdrawal in high water-stress areas</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>The portion of the above that was drawn from a site located in a region already short of water.</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Check your site address(es) against a public water-stress map (e.g. WRI Aqueduct, free online tool) — if any site falls in a high-stress area, report that site’s withdrawal separately.</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>VSME B6-2 §35</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="46.25" customHeight="1" s="6">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Water consumption (E3-4)</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>E3-4</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Water consumption</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Water you withdrew but did not return to the environment (i.e. water "used up" in production, not just passed through).</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>Subtract your metered wastewater discharge volume from your total withdrawal above — both figures usually already exist on your water and drainage bills.</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>VSME B6-3 §36</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="35.05" customHeight="1" s="6">
+    <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Resource inflows (E5-2)</t>
@@ -1762,7 +2061,7 @@
           <t>A short write-up from your production/operations team of efficiency improvements already made — supported by your E3/E5 usage figures over time.</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1778,7 +2077,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="46.25" customHeight="1" s="6">
+    <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Resource inflows (E5-2)</t>
@@ -1804,7 +2103,7 @@
           <t>From your procurement records — the share of purchased materials that are recycled/recovered content, usually stated by your packaging/material supplier.</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1820,7 +2119,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="35.05" customHeight="1" s="6">
+    <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Resource inflows (E5-2)</t>
@@ -1846,7 +2145,7 @@
           <t>From your product/packaging design team — describe design choices already made (e.g. mono-material packaging, recyclable trays).</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1862,7 +2161,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="35.05" customHeight="1" s="6">
+    <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Resource inflows (E5-2)</t>
@@ -1888,7 +2187,7 @@
           <t>From operations — many seafood processors already do this (e.g. selling offcuts for fishmeal); just document what already happens.</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -1904,175 +2203,175 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="35.05" customHeight="1" s="6">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Resource outflows (E5-4)</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>E5-4</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Disclosure of information on material resource inflows</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>A general description of the materials that flow into your production (raw fish, packaging, ingredients).</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>From your procurement/production records — a descriptive overview, not a new measurement system.</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>ESRS E5-4_01</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>LCA methodologies, ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="23.85" customHeight="1" s="6">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Resource outflows (E5-4)</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>E5-4</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Overall total weight of products and technical and biological material…</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>The total weight of everything you bought in and used to make your products in the year.</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Sum of your goods-in weighbridge or procurement records for the year.</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>ESRS E5-4_02</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>LCA methodologies, ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="35.05" customHeight="1" s="6">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Resource outflows (E5-4)</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>E5-4</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Percentage of biological materials (and biofuels used for non-energy p…</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>What share of your material inputs are biological in origin (e.g. fish, plant-based ingredients) rather than synthetic/mineral.</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>From the same procurement data — split by material type, which your goods-in records usually already categorise.</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>ESRS E5-4_03</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>LCA methodologies, ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="35.05" customHeight="1" s="6">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Resource outflows (E5-4)</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>E5-4</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>The absolute weight of secondary reused or recycled components, second…</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>The weight of recycled/recovered material (including packaging) you used, as opposed to virgin material.</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>From your packaging/material supplier specifications — recycled-content percentages are usually stated on the product data sheet.</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>ESRS E5-4_04</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>LCA methodologies, ISO 14001</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="46.25" customHeight="1" s="6">
+    <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Waste (E5-5)</t>
@@ -2098,7 +2397,7 @@
           <t>Ask your waste contractor for their annual weighbridge/collection report, broken down by hazardous vs non-hazardous — they already record this for their own permits.</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -2114,7 +2413,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="46.25" customHeight="1" s="6">
+    <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Waste (E5-5)</t>
@@ -2140,7 +2439,7 @@
           <t>Same waste-contractor report as above; hazardous waste additionally requires a signed consignment/transfer note under EU waste law, which gives you an exact figure.</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -2156,7 +2455,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="46.25" customHeight="1" s="6">
+    <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Waste (E5-5)</t>
@@ -2182,7 +2481,7 @@
           <t>Your waste contractor’s report again — ask them to split "recycled/recovered" from "disposed" tonnage; most contracts already track this for their own compliance reporting.</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -2198,175 +2497,175 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="35.05" customHeight="1" s="6">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Business-conduct policy (G1-1)</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>G1-1</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Description of how the undertaking establishes, develops, promotes and…</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>A description of how you build and reinforce an ethical culture in your company (values, training, leadership example).</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>From HR/management — describe existing practices (staff handbook, induction training, code of conduct communication).</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>ESRS G1-1_01</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="46.25" customHeight="1" s="6">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Business-conduct policy (G1-1)</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>G1-1</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Description of the mechanisms for identifying, reporting and investiga…</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>A description of how staff can report wrongdoing (a whistleblowing channel) and how such reports get investigated.</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>From HR/legal — describe your existing reporting channel (e.g. a hotline, an email box, an external ethics line) and who investigates; if none exists, this flags a gap.</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>ESRS G1-1_02</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="23.85" customHeight="1" s="6">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Business-conduct policy (G1-1)</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>G1-1</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>No policies on anti-corruption or anti-bribery consistent with United …</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>A statement confirming whether or not you have an anti-corruption/anti-bribery policy in place.</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>Check with legal/management whether such a policy document exists.</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>ESRS G1-1_03</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="23.85" customHeight="1" s="6">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Business-conduct policy (G1-1)</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>G1-1</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Timetable for implementation of policies on anti-corruption or anti-br…</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>If you don’t yet have such a policy, when you plan to put one in place.</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>A management commitment/date, only needed if the previous answer was "no policy in place".</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>ESRS G1-1_04</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="35.05" customHeight="1" s="6">
+    <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Anti-corruption (G1-3)</t>
@@ -2392,7 +2691,7 @@
           <t>From legal/finance — describe existing internal controls; most companies already have some of these (e.g. dual sign-off on payments).</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2408,7 +2707,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="35.05" customHeight="1" s="6">
+    <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Anti-corruption (G1-3)</t>
@@ -2434,7 +2733,7 @@
           <t>A governance/organisational fact — confirm with legal who would investigate and whether they sit outside the relevant management line.</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2450,7 +2749,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="23.85" customHeight="1" s="6">
+    <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Anti-corruption (G1-3)</t>
@@ -2476,7 +2775,7 @@
           <t>From governance/legal — describe existing reporting lines (e.g. to the board or owner).</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2492,7 +2791,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="35.05" customHeight="1" s="6">
+    <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Anti-corruption (G1-3)</t>
@@ -2518,7 +2817,7 @@
           <t>A management commitment, only needed if no procedure exists yet.</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2534,91 +2833,91 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="35.05" customHeight="1" s="6">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Corruption incidents (G1-4)</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>G1-4</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Convictions for corruption/bribery</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Whether your company (or its people, acting for it) has been convicted in court for bribery or corruption.</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>This should already be visible to your legal/compliance function or company secretary — if there are none, the answer is simply zero.</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>VSME B11-1 §43</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="23.85" customHeight="1" s="6">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Corruption incidents (G1-4)</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>G1-4</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Fines for corruption/bribery</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>The total value of any fines imposed for bribery or corruption offences.</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Same source as above — your legal/finance function will hold any such fine on record.</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>VSME B11-2 §43</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="35.05" customHeight="1" s="6">
+    <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Political influence (G1-5)</t>
@@ -2644,7 +2943,7 @@
           <t>A governance fact — name the responsible person/role, or state that no such activity/role exists (common for most seafood SMEs).</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2660,7 +2959,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="23.85" customHeight="1" s="6">
+    <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Political influence (G1-5)</t>
@@ -2686,7 +2985,7 @@
           <t>From finance — check your accounts for any such payments; most SMEs will report none.</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2702,7 +3001,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="23.85" customHeight="1" s="6">
+    <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Political influence (G1-5)</t>
@@ -2728,7 +3027,7 @@
           <t>From your accounts — likely zero for most seafood SMEs.</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2744,7 +3043,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="35.05" customHeight="1" s="6">
+    <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Political influence (G1-5)</t>
@@ -2770,7 +3069,7 @@
           <t>From finance/operations — likely zero for most seafood SMEs.</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -2786,175 +3085,175 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="46.25" customHeight="1" s="6">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Own-workforce policy (S1-1)</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>S1-1</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Policies to manage material impacts, risks and opportunities related t…</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Whether you have a written HR/labour policy covering your own staff (and any groups of staff needing special attention, e.g. seasonal or migrant workers).</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Check with HR whether an employment/labour policy or handbook exists and what it covers; most processors already have one for legal-compliance reasons.</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-1_01</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>ISO 45001, AA1000</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="46.25" customHeight="1" s="6">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Own-workforce policy (S1-1)</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>S1-1</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Description of relevant human rights policy commitments relevant to ow…</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Whether your policy explicitly commits to respecting workers’ basic rights (fair pay, no forced/child labour, freedom of association).</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Check whether your HR policy or code of conduct references these commitments explicitly (many customer codes of conduct, e.g. Sedex/SMETA, already require this wording).</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-1_03</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>ISO 45001, AA1000</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="35.05" customHeight="1" s="6">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Own-workforce policy (S1-1)</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>S1-1</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to respect for human rights…</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>A description of how, in practice, you make sure your own staff’s labour rights are respected day to day.</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>From HR — describe existing practices (contracts, working-time tracking, grievance access).</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-1_04</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>ISO 45001, AA1000</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="23.85" customHeight="1" s="6">
-      <c r="A59" s="9" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Own-workforce policy (S1-1)</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>S1-1</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to engagement with people i…</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>A description of how you talk to and involve your staff (works council, regular meetings, surveys).</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>From HR/management — describe existing channels; if none exist, this flags where to start.</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-1_05</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>ISO 45001, AA1000</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="57.45" customHeight="1" s="6">
+    <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Health &amp; safety (S1-14)</t>
@@ -2980,7 +3279,7 @@
           <t>Pull this from your existing accident/incident log (most EU countries require you to keep one for occupational-safety law anyway); the rate is accidents divided by total hours worked, ×1,000,000 (standard formula).</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -2996,7 +3295,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="35.05" customHeight="1" s="6">
+    <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Health &amp; safety (S1-14)</t>
@@ -3022,7 +3321,7 @@
           <t>Same incident log — this is simply a required, separately-flagged line item, not new data collection.</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -3038,175 +3337,175 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="35.05" customHeight="1" s="6">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>Human-rights incidents (S1-17)</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>S1-17</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Number of incidents of discrimination [table]</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>How many discrimination complaints or incidents were recorded, broken down by type/category.</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>From your HR grievance log — this only requires you to already have the S1-3 complaints channel in place and recording outcomes.</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-17_01</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="23.85" customHeight="1" s="6">
-      <c r="A63" s="9" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Human-rights incidents (S1-17)</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>S1-17</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Number of incidents of discrimination</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>The total count of discrimination incidents in the year.</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Same HR grievance log — a total, not a new data source.</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-17_02</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="35.05" customHeight="1" s="6">
-      <c r="A64" s="9" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Human-rights incidents (S1-17)</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>S1-17</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Number of complaints filed through channels for people in own workforc…</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>How many complaints of any kind (not just discrimination) came through your worker grievance channels.</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Same HR grievance log.</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-17_03</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="35.05" customHeight="1" s="6">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Human-rights incidents (S1-17)</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>S1-17</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Number of complaints filed to National Contact Points for OECD Multina…</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Whether any complaint about you was escalated to the OECD’s national grievance body (a formal, external process — rare for most SMEs).</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>Check with legal; for the large majority of seafood SMEs this will be zero, since it applies mainly to multinational-scale disputes.</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-17_04</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="46.25" customHeight="1" s="6">
+    <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Worker engagement (S1-2)</t>
@@ -3232,7 +3531,7 @@
           <t>From HR/management — describe an example (e.g. safety committee feedback leading to a process change), or note this as a gap if it doesn’t happen yet.</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3248,7 +3547,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="35.05" customHeight="1" s="6">
+    <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Worker engagement (S1-2)</t>
@@ -3274,7 +3573,7 @@
           <t>A factual HR statement.</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3290,7 +3589,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="35.05" customHeight="1" s="6">
+    <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Worker engagement (S1-2)</t>
@@ -3316,7 +3615,7 @@
           <t>From HR — describe your existing cadence (e.g. monthly toolbox talks, annual survey).</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3332,7 +3631,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="35.05" customHeight="1" s="6">
+    <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>Worker engagement (S1-2)</t>
@@ -3358,7 +3657,7 @@
           <t>Name the role (e.g. HR manager, site manager) — an organisational fact, not new data.</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3374,175 +3673,175 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="46.25" customHeight="1" s="6">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>Grievance channels (S1-3)</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>S1-3</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach to and processes for providing or contr…</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>How you put things right if your company has caused harm to one of your own workers.</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>From HR/legal — describe your existing remediation process (e.g. disciplinary/compensation procedures), or note as a gap if none exists.</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-3_01</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="35.05" customHeight="1" s="6">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>Grievance channels (S1-3)</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>S1-3</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Disclosure of specific channels in place for its own workforce to rais…</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>What concrete channels staff have to raise a concern (hotline, HR office hours, suggestion box, union rep).</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>List your existing channels — most processors already have at least a direct-to-HR route required by labour law.</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-3_02</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="35.05" customHeight="1" s="6">
-      <c r="A72" s="9" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>Grievance channels (S1-3)</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>S1-3</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>Grievance or complaints handling mechanisms related to employee matter…</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>A simple yes/no confirming a formal complaints process exists.</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>A factual HR statement.</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-3_05</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="35.05" customHeight="1" s="6">
-      <c r="A73" s="9" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Grievance channels (S1-3)</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>S1-3</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Disclosure of processes through which undertaking supports or requires…</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>How you make sure these channels are actually accessible (e.g. posted in the break room, available in workers’ own language).</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>From HR — describe how the channels above are communicated/made accessible in practice.</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>ESRS S1-3_06</t>
         </is>
       </c>
-      <c r="H73" s="9" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="23.85" customHeight="1" s="6">
+    <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
           <t>Action on workforce (S1-4)</t>
@@ -3568,7 +3867,7 @@
           <t>From HR/H&amp;S — list concrete actions already under way (e.g. new PPE, revised shift patterns).</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3584,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="35.05" customHeight="1" s="6">
+    <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Action on workforce (S1-4)</t>
@@ -3610,7 +3909,7 @@
           <t>From HR/legal — report on any actual case and how it was resolved; report none if there were no such cases.</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3626,7 +3925,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="35.05" customHeight="1" s="6">
+    <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Action on workforce (S1-4)</t>
@@ -3652,7 +3951,7 @@
           <t>From HR — list existing staff-benefit initiatives.</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3668,7 +3967,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="35.05" customHeight="1" s="6">
+    <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Action on workforce (S1-4)</t>
@@ -3694,7 +3993,7 @@
           <t>From HR — describe any tracking already done (e.g. repeat safety-incident rates, staff survey scores); flag as a gap if not yet tracked.</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3710,133 +4009,133 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="23.85" customHeight="1" s="6">
-      <c r="A78" s="9" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>Workforce profile (S1-6)</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>S1-6</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Employees by contract type</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>How many of your staff are on permanent vs temporary/fixed-term contracts.</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>Straight from your HR/payroll system — every employee record already carries a contract type.</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F78" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>VSME B8-1 §39(a)</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr">
         <is>
           <t>ISO 45001</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="23.85" customHeight="1" s="6">
-      <c r="A79" s="9" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>Workforce profile (S1-6)</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>S1-6</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Employees by gender</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>How many of your staff are men, women, or other/undisclosed.</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Straight from your HR/payroll system.</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>VSME B8-2 §39(b)</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>ISO 45001</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="35.05" customHeight="1" s="6">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>Workforce profile (S1-6)</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>S1-6</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Employee turnover rate</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>What share of your workforce left (voluntarily or not) during the year.</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>Leavers during the year ÷ average headcount during the year — both numbers already sit in your HR/payroll system.</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>VSME B8-4 §40</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>ISO 45001</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="35.05" customHeight="1" s="6">
+    <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Diversity (S1-9)</t>
@@ -3862,7 +4161,7 @@
           <t>From HR/payroll — filter your existing employee records by seniority level and gender.</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3878,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="23.85" customHeight="1" s="6">
+    <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Diversity (S1-9)</t>
@@ -3904,7 +4203,7 @@
           <t>A calculation from the figure above.</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3920,7 +4219,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="23.85" customHeight="1" s="6">
+    <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Diversity (S1-9)</t>
@@ -3946,7 +4245,7 @@
           <t>From HR/payroll — a simple age-band filter on existing records.</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -3962,7 +4261,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="23.85" customHeight="1" s="6">
+    <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Diversity (S1-9)</t>
@@ -3988,7 +4287,7 @@
           <t>Same age-band filter on existing HR records.</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -4004,175 +4303,175 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="57.45" customHeight="1" s="6">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>Value-chain workers – policy (S2-1)</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>S2-1</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Description of relevant human rights policy commitments relevant to va…</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>Whether your policy commitments on labour/human rights also extend to workers in your supply chain (e.g. at your fishing/farming suppliers), not just your own staff.</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>Check whether your supplier code of conduct or purchasing policy states this explicitly — many certification schemes (MSC/ASC/SMETA) already require suppliers to meet baseline labour standards.</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-1_01</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="35.05" customHeight="1" s="6">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>Value-chain workers – policy (S2-1)</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>S2-1</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to respect for human rights…</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>How, in practice, you make sure suppliers respect their own workers’ rights.</t>
         </is>
       </c>
-      <c r="E86" s="9" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>From procurement — describe your supplier vetting/audit process (e.g. requiring SMETA/BSCI audits).</t>
         </is>
       </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-1_02</t>
         </is>
       </c>
-      <c r="H86" s="9" t="inlineStr">
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="35.05" customHeight="1" s="6">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>Value-chain workers – policy (S2-1)</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>S2-1</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to engagement with value ch…</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>Whether and how you engage with workers further down your supply chain (not just your direct supplier company).</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>From procurement/sustainability — describe any worker-voice mechanism used in your supply chain audits, or note this as an area not yet covered.</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-1_03</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="35.05" customHeight="1" s="6">
-      <c r="A88" s="9" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>Value-chain workers – policy (S2-1)</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>S2-1</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to measures to provide and…</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>How harm to a supplier’s workers would get remedied if it were found.</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>From procurement — describe your corrective-action process when an audit finds a labour issue at a supplier.</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-1_04</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="35.05" customHeight="1" s="6">
+    <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Value-chain – engagement (S2-2)</t>
@@ -4198,7 +4497,7 @@
           <t>From procurement — describe an example, or note as a gap.</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -4214,7 +4513,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="35.05" customHeight="1" s="6">
+    <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Value-chain – engagement (S2-2)</t>
@@ -4240,7 +4539,7 @@
           <t>A factual statement based on your existing audit process (e.g. worker interviews as part of a SMETA audit count as this).</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -4256,7 +4555,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="35.05" customHeight="1" s="6">
+    <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Value-chain – engagement (S2-2)</t>
@@ -4282,7 +4581,7 @@
           <t>From procurement — describe your existing audit/engagement schedule.</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -4298,7 +4597,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="23.85" customHeight="1" s="6">
+    <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Value-chain – engagement (S2-2)</t>
@@ -4324,7 +4623,7 @@
           <t>Name the role (e.g. head of procurement/sustainability).</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>ESRS</t>
         </is>
@@ -4340,175 +4639,175 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="23.85" customHeight="1" s="6">
-      <c r="A93" s="9" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>Value-chain – remediation (S2-3)</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>S2-3</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach to and processes for providing or contr…</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>How you help fix harm found at a supplier, even though you didn’t cause it directly.</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>From procurement — describe your corrective-action-plan process with suppliers.</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-3_01</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="35.05" customHeight="1" s="6">
-      <c r="A94" s="9" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>Value-chain – remediation (S2-3)</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>S2-3</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Disclosure of specific channels in place for value chain workers to ra…</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Whether workers at your suppliers have any way to raise a concern directly with you (not just through their employer).</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>Check whether your certification scheme (e.g. GDST/MSC/ASC) or a shared grievance line (e.g. Issara, Ulula) already gives this access.</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-3_02</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="35.05" customHeight="1" s="6">
-      <c r="A95" s="9" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>Value-chain – remediation (S2-3)</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>S2-3</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Disclosure of processes through which undertaking supports or requires…</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>How you make sure such channels are actually usable by supply-chain workers (language, awareness).</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>From procurement/sustainability — describe existing supplier-training or communication requirements.</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-3_03</t>
         </is>
       </c>
-      <c r="H95" s="9" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="23.85" customHeight="1" s="6">
-      <c r="A96" s="9" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>Value-chain – remediation (S2-3)</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>S2-3</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Disclosure of how issues raised and addressed are tracked and monitore…</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>How you track that issues raised actually get resolved.</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>From procurement — describe your corrective-action tracking log, if one exists.</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>ESRS S2-3_04</t>
         </is>
       </c>
-      <c r="H96" s="9" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>AA1000, Supplier portals / data-exchange platforms</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="46.25" customHeight="1" s="6">
+    <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Biodiversity &amp; ecosystems (E4)</t>
@@ -4534,7 +4833,7 @@
           <t>Check your site addresses against a public biodiversity map (e.g. the EU’s Natura 2000 Viewer, free online) — a one-off desk check per site, not ongoing monitoring.</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -4550,7 +4849,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="46.25" customHeight="1" s="6">
+    <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Biodiversity &amp; ecosystems (E4)</t>
@@ -4576,7 +4875,7 @@
           <t>From your own site plans/facility records — most sites already have this in planning permission or facility-management documents.</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -4592,7 +4891,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="46.25" customHeight="1" s="6">
+    <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>Biodiversity &amp; ecosystems (E4)</t>
@@ -4618,7 +4917,7 @@
           <t>From your own grounds/facility records; if none exists yet, this is simply reported as zero.</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>VSME</t>
         </is>
@@ -4634,175 +4933,175 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="35.05" customHeight="1" s="6">
-      <c r="A100" s="9" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; food safety (S4)</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; end-users (S4)</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>Policies to manage material impacts, risks and opportunities related t…</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Whether you have a policy covering the impact your products have on the people who eat them (food safety, allergens, labelling).</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Check with quality/food-safety — most processors already hold a food-safety policy (e.g. under BRCGS/IFS/FSSC 22000) that covers this.</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>ESRS S4-1_01</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Food-safety management systems (BRCGS / IFS Food / FSSC 22000)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="35.05" customHeight="1" s="6">
-      <c r="A101" s="9" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; food safety (S4)</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; end-users (S4)</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>Description of relevant human rights policy commitments relevant to co…</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Whether your policy commits to consumers’ basic rights (safe, accurately-labelled food; access to information).</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Check your existing food-safety/quality policy for this wording.</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>ESRS S4-1_02</t>
         </is>
       </c>
-      <c r="H101" s="9" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>Food-safety management systems (BRCGS / IFS Food / FSSC 22000)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="35.05" customHeight="1" s="6">
-      <c r="A102" s="9" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; food safety (S4)</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; end-users (S4)</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to respect for human rights…</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>How, in practice, you protect consumers (traceability, allergen labelling, recall procedures).</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>From quality — describe existing food-safety management-system practices.</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
         <is>
           <t>ESRS S4-1_03</t>
         </is>
       </c>
-      <c r="H102" s="9" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>Food-safety management systems (BRCGS / IFS Food / FSSC 22000)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="35.05" customHeight="1" s="6">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; food safety (S4)</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Consumers &amp; end-users (S4)</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>Disclosure of general approach in relation to engagement with consumer…</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>How you get and use feedback from consumers (complaints line, market research).</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>From quality/customer service — describe your existing consumer-complaints process.</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>ESRS</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>ESRS</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>ESRS S4-1_04</t>
         </is>
       </c>
-      <c r="H103" s="9" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>Food-safety management systems (BRCGS / IFS Food / FSSC 22000)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="57.45" customHeight="1" s="6">
+    <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -4828,7 +5127,7 @@
           <t>Your own inventory/ERP system already assigns a SKU to every product; a GTIN is the barcode number your customer or GS1 (the standards body) assigns — no new system needed if you already run a stock system.</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F104" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -4844,7 +5143,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="57.45" customHeight="1" s="6">
+    <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -4870,7 +5169,7 @@
           <t>This is your production/batch number — most processors already assign one per intake batch; make sure it is retained and passed on when the product changes hands (to your customer, or from your supplier to you).</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -4886,7 +5185,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="57.45" customHeight="1" s="6">
+    <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -4912,7 +5211,7 @@
           <t>Your existing goods-in/weighbridge or production records.</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F106" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -4928,7 +5227,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="57.45" customHeight="1" s="6">
+    <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -4954,7 +5253,7 @@
           <t>Your supplier’s catch/harvest certificate or landing declaration should already state the scientific name; if not, it is a standard lookup from the common name via FAO species codes.</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -4970,7 +5269,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="57.45" customHeight="1" s="6">
+    <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -4996,7 +5295,7 @@
           <t>From the catch certificate (wild) or farm/site registration (aquaculture) provided by your supplier — this must be passed on unchanged, not re-estimated.</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="F108" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -5012,7 +5311,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="57.45" customHeight="1" s="6">
+    <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -5038,7 +5337,7 @@
           <t>Your certifier (MSC/ASC) issues chain-of-custody certificates per site/batch — check your own or your supplier’s certificate number and validity dates.</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -5054,7 +5353,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="57.45" customHeight="1" s="6">
+    <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
           <t>Supply-chain traceability</t>
@@ -5080,7 +5379,7 @@
           <t>Vessel registration number from the catch certificate, or farm/site ID from your aquaculture supplier’s records.</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F110" s="14" t="inlineStr">
         <is>
           <t>GDST</t>
         </is>
@@ -5096,49 +5395,49 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="57.45" customHeight="1" s="6">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>Wild-stock sourcing</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Wild-stock status / sustainable wild sourcing</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>(no separate datapoints)</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>Evidenced entirely through your Traceability datapoints (species, origin, chain-of-custody certification) -- no separate data to build.</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>Complete the Supply-chain traceability datapoints; this topic is covered automatically.</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G111" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr">
+      <c r="H111" s="7" t="inlineStr">
         <is>
           <t>GDST, MSC chain-of-custody certification</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="46.25" customHeight="1" s="6">
+    <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
           <t>Feed &amp; marine ingredients</t>
@@ -5180,93 +5479,92 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="68.65000000000001" customHeight="1" s="6">
-      <c r="A113" s="9" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>Animal health &amp; AMU</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Animal health &amp; welfare (incl. antimicrobial use)</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>(no separate datapoints)</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>Evidenced entirely through your Traceability datapoints (species, origin, chain-of-custody certification) -- no separate data to build.</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>Complete the Supply-chain traceability datapoints; this topic is covered automatically.</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="9" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>GDST, ASC chain-of-custody certification</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <autoFilter ref="A1:H113"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="5" min="1" max="1"/>
-    <col width="22" customWidth="1" style="5" min="2" max="2"/>
-    <col width="50" customWidth="1" style="5" min="3" max="3"/>
-    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="6">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>What it helps you do</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Already in thesis instrument catalogue?</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="23.85" customHeight="1" s="6">
+    <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>GHG Protocol</t>
@@ -5288,7 +5586,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="23.85" customHeight="1" s="6">
+    <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>ISO 14064</t>
@@ -5310,7 +5608,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="23.85" customHeight="1" s="6">
+    <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>LCA methodologies</t>
@@ -5332,7 +5630,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="6">
+    <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>PEF / PEFCR</t>
@@ -5354,51 +5652,51 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" s="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>ISAE 3000</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Assurance</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>The assurance standard auditors use for limited/reasonable assurance over CSRD/VSME disclosures.</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Yes -- Appendix A</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="6">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>AA1000</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Assurance</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Stakeholder-engagement and assurance standard -- directly useful for the ESRS engagement/grievance datapoints.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Yes -- Appendix A</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="23.85" customHeight="1" s="6">
+    <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>ISO 14001</t>
@@ -5420,7 +5718,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="23.85" customHeight="1" s="6">
+    <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>ISO 45001</t>
@@ -5442,7 +5740,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="6">
+    <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>ISO 50001</t>
@@ -5464,29 +5762,29 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="23.85" customHeight="1" s="6">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Supplier portals / data-exchange platforms</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Data infrastructure</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Where value-chain data (S2, traceability) is typically exchanged with customers.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Yes -- Appendix A</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="35.05" customHeight="1" s="6">
+    <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>GDST</t>
@@ -5508,29 +5806,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="23.85" customHeight="1" s="6">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>MSC / ASC chain-of-custody certification</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Third-party certification evidencing wild-stock (MSC) or farmed (ASC) sourcing claims.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Yes -- Appendix A (Tier 2)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="23.85" customHeight="1" s="6">
+    <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>UN Global Compact (Principle 10)</t>
@@ -5552,31 +5850,30 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="23.85" customHeight="1" s="6">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Food-safety management systems (BRCGS / IFS Food / FSSC 22000)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Food-safety certification schemes that already cover most S4 consumer-protection datapoints.</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Yes -- Appendix A (Tier 2/3)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <autoFilter ref="A1:D15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>